--- a/exports/study_2026-05-12/TMC_NBeltLineRd_ETownEastBlvd_2026-05-12.xlsx
+++ b/exports/study_2026-05-12/TMC_NBeltLineRd_ETownEastBlvd_2026-05-12.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17026</v>
+        <v>17624</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1464</v>
+        <v>1450</v>
       </c>
       <c r="C7" t="n">
         <v>1120</v>
       </c>
       <c r="D7" t="n">
-        <v>1679</v>
+        <v>1598</v>
       </c>
       <c r="E7" t="n">
         <v>7</v>
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4270</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="8">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5033</v>
+        <v>5263</v>
       </c>
       <c r="C8" t="n">
         <v>1288</v>
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6328</v>
+        <v>6558</v>
       </c>
     </row>
     <row r="9">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4004</v>
+        <v>4499</v>
       </c>
       <c r="C9" t="n">
         <v>103</v>
@@ -570,13 +570,13 @@
         <v>647</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4831</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="10">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>690</v>
+        <v>664</v>
       </c>
       <c r="C10" t="n">
         <v>145</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1597</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="11">
@@ -611,22 +611,22 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>11191</v>
+        <v>11876</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>2656</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>3091</v>
+        <v>3010</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>17026</v>
+        <v>17624</v>
       </c>
     </row>
   </sheetData>
@@ -651,7 +651,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>raw events: 17026</t>
+          <t>raw events: 17624</t>
         </is>
       </c>
     </row>
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1464</v>
+        <v>1450</v>
       </c>
       <c r="C3" t="n">
         <v>1120</v>
       </c>
       <c r="D3" t="n">
-        <v>1679</v>
+        <v>1598</v>
       </c>
       <c r="E3" t="n">
         <v>7</v>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4270</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="4">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5033</v>
+        <v>5263</v>
       </c>
       <c r="C4" t="n">
         <v>1288</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6328</v>
+        <v>6558</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4004</v>
+        <v>4499</v>
       </c>
       <c r="C5" t="n">
         <v>103</v>
@@ -758,13 +758,13 @@
         <v>647</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4831</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="6">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>690</v>
+        <v>664</v>
       </c>
       <c r="C6" t="n">
         <v>145</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1597</v>
+        <v>1571</v>
       </c>
     </row>
   </sheetData>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C3" t="n">
         <v>47</v>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -956,19 +956,19 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K3" t="n">
         <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C4" t="n">
         <v>60</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -1014,19 +1014,19 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K4" t="n">
         <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>712</v>
+        <v>749</v>
       </c>
     </row>
     <row r="5">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C5" t="n">
         <v>85</v>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1072,19 +1072,19 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K5" t="n">
         <v>46</v>
       </c>
       <c r="L5" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O5" t="n">
         <v>9</v>
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>828</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C6" t="n">
         <v>77</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1130,13 +1130,13 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6" t="n">
         <v>42</v>
       </c>
       <c r="L6" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="7">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C7" t="n">
         <v>48</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1188,19 +1188,19 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K7" t="n">
         <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C8" t="n">
         <v>39</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -1246,19 +1246,19 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
         <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O8" t="n">
         <v>9</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>636</v>
+        <v>659</v>
       </c>
     </row>
     <row r="9">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C9" t="n">
         <v>41</v>
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -1304,19 +1304,19 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K9" t="n">
         <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="C10" t="n">
         <v>59</v>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
@@ -1362,19 +1362,19 @@
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>668</v>
+        <v>705</v>
       </c>
     </row>
     <row r="11">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C11" t="n">
         <v>42</v>
@@ -1408,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K11" t="n">
         <v>40</v>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>482</v>
+        <v>497</v>
       </c>
     </row>
     <row r="12">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C12" t="n">
         <v>52</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K12" t="n">
         <v>38</v>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>486</v>
+        <v>513</v>
       </c>
     </row>
     <row r="13">
@@ -1524,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1533,10 +1533,10 @@
         <v>32</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K13" t="n">
         <v>31</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>540</v>
+        <v>554</v>
       </c>
     </row>
     <row r="14">
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" t="n">
         <v>44</v>
@@ -1582,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K14" t="n">
         <v>37</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O14" t="n">
         <v>7</v>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>549</v>
+        <v>564</v>
       </c>
     </row>
     <row r="15">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C15" t="n">
         <v>47</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1649,10 +1649,10 @@
         <v>33</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K15" t="n">
         <v>48</v>
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O15" t="n">
         <v>5</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>572</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C16" t="n">
         <v>58</v>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K16" t="n">
         <v>37</v>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O16" t="n">
         <v>7</v>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C17" t="n">
         <v>37</v>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
@@ -1765,10 +1765,10 @@
         <v>33</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K17" t="n">
         <v>56</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
         <v>7</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>557</v>
+        <v>583</v>
       </c>
     </row>
     <row r="18">
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C18" t="n">
         <v>48</v>
@@ -1814,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="G18" t="n">
         <v>4</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O18" t="n">
         <v>7</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>576</v>
+        <v>615</v>
       </c>
     </row>
     <row r="19">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C19" t="n">
         <v>69</v>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="G19" t="n">
         <v>13</v>
@@ -1884,7 +1884,7 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K19" t="n">
         <v>58</v>
@@ -1896,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O19" t="n">
         <v>9</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>876</v>
+        <v>907</v>
       </c>
     </row>
     <row r="20">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C20" t="n">
         <v>39</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G20" t="n">
         <v>4</v>
@@ -1939,10 +1939,10 @@
         <v>14</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="K20" t="n">
         <v>65</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>700</v>
+        <v>711</v>
       </c>
     </row>
     <row r="21">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C21" t="n">
         <v>65</v>
@@ -1988,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="G21" t="n">
         <v>14</v>
@@ -1997,10 +1997,10 @@
         <v>27</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="K21" t="n">
         <v>85</v>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="O21" t="n">
         <v>5</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1024</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="22">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="C22" t="n">
         <v>47</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="G22" t="n">
         <v>14</v>
@@ -2058,7 +2058,7 @@
         <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K22" t="n">
         <v>54</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>883</v>
+        <v>931</v>
       </c>
     </row>
     <row r="23">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="C23" t="n">
         <v>64</v>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="G23" t="n">
         <v>7</v>
@@ -2116,7 +2116,7 @@
         <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="K23" t="n">
         <v>71</v>
@@ -2128,7 +2128,7 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O23" t="n">
         <v>6</v>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>888</v>
+        <v>928</v>
       </c>
     </row>
     <row r="24">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="C24" t="n">
         <v>62</v>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
@@ -2174,7 +2174,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
         <v>69</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>903</v>
+        <v>966</v>
       </c>
     </row>
     <row r="25">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C25" t="n">
         <v>52</v>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="G25" t="n">
         <v>8</v>
@@ -2232,7 +2232,7 @@
         <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K25" t="n">
         <v>64</v>
@@ -2244,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>896</v>
+        <v>930</v>
       </c>
     </row>
     <row r="26">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="C26" t="n">
         <v>62</v>
@@ -2278,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="G26" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>896</v>
+        <v>950</v>
       </c>
     </row>
     <row r="27">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>5033</v>
+        <v>5263</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>1288</v>
@@ -2336,7 +2336,7 @@
         <v>4</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>4004</v>
+        <v>4499</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>103</v>
@@ -2345,22 +2345,22 @@
         <v>647</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>1464</v>
+        <v>1450</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>1120</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1679</v>
+        <v>1598</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>7</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>690</v>
+        <v>664</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>145</v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>17026</v>
+        <v>17624</v>
       </c>
     </row>
   </sheetData>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>17026</v>
+        <v>17624</v>
       </c>
     </row>
     <row r="2">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17026</v>
+        <v>17624</v>
       </c>
     </row>
   </sheetData>
